--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487182_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487182_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>13.2403</v>
+        <v>13.7082</v>
       </c>
       <c r="E2" t="n">
-        <v>11.9508</v>
+        <v>12.1511</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2895</v>
+        <v>1.5572</v>
       </c>
       <c r="G2" t="n">
         <v>10.01</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7284</v>
+        <v>1.1964</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9029</v>
+        <v>1.1032</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1745</v>
+        <v>0.0931</v>
       </c>
       <c r="V2" t="n">
         <v>0.5717</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.6243</v>
+        <v>7.6847</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8473</v>
+        <v>4.7472</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7769</v>
+        <v>2.9376</v>
       </c>
       <c r="G3" t="n">
         <v>4.9136</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5526</v>
+        <v>0.6131</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4891</v>
+        <v>0.389</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0634</v>
+        <v>0.2241</v>
       </c>
       <c r="V3" t="n">
         <v>0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7253</v>
+        <v>5.9349</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7513</v>
+        <v>1.4522</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9741</v>
+        <v>4.4827</v>
       </c>
       <c r="G4" t="n">
         <v>4.8781</v>
@@ -766,13 +766,13 @@
         <v>2.1231</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5665</v>
+        <v>0.6431</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4614</v>
+        <v>0.2396</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1051</v>
+        <v>0.4035</v>
       </c>
       <c r="V4" t="n">
         <v>1.1857</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2106</v>
+        <v>4.2175</v>
       </c>
       <c r="E5" t="n">
-        <v>3.801</v>
+        <v>3.7008</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4096</v>
+        <v>0.5167</v>
       </c>
       <c r="G5" t="n">
         <v>1.5701</v>
@@ -844,13 +844,13 @@
         <v>1.158</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7839</v>
+        <v>0.7909</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7562</v>
+        <v>0.656</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0277</v>
+        <v>0.1348</v>
       </c>
       <c r="V5" t="n">
         <v>0.6985</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. TAVERAS RAFAEL</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8544</v>
+        <v>1.8126</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3016</v>
+        <v>0.3122</v>
       </c>
       <c r="F6" t="n">
-        <v>3.156</v>
+        <v>1.5005</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6742</v>
+        <v>0.3045</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0516</v>
+        <v>0.7329</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7258</v>
+        <v>-0.4284</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6346000000000001</v>
+        <v>0.157</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2462</v>
+        <v>0.1656</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6116</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3089</v>
+        <v>0.1474</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1946</v>
+        <v>0.5673</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1142</v>
+        <v>-0.4199</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>1.158</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5542</v>
+        <v>0.7205</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9652</v>
+        <v>0.5255</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5889</v>
+        <v>0.195</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3281</v>
+        <v>-0.3704</v>
       </c>
       <c r="W6" t="n">
-        <v>1.228</v>
+        <v>-0.3704</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>M. CARRETERO GARCÍA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4517</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1119</v>
+        <v>1.2064</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3398</v>
+        <v>-0.487</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3045</v>
+        <v>0.7075</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7329</v>
+        <v>-0.8341</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4284</v>
+        <v>1.5416</v>
       </c>
       <c r="J7" t="n">
-        <v>0.157</v>
+        <v>2.3961</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1656</v>
+        <v>0.4347</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.9614</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1474</v>
+        <v>-1.6886</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5673</v>
+        <v>-1.2688</v>
       </c>
       <c r="O7" t="n">
         <v>-0.4199</v>
       </c>
       <c r="P7" t="n">
-        <v>1.158</v>
+        <v>-0.579</v>
       </c>
       <c r="Q7" t="n">
+        <v>-1.9301</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3511</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.5486</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7403</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.1917</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.0422</v>
+      </c>
+      <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="n">
-        <v>1.158</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3596</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.3252</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.0344</v>
-      </c>
-      <c r="V7" t="n">
-        <v>-0.3704</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.3704</v>
-      </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>V. TAVERAS RAFAEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1365</v>
+        <v>0.6959</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1139</v>
+        <v>-1.6034</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0226</v>
+        <v>2.2994</v>
       </c>
       <c r="G8" t="n">
-        <v>2.136</v>
+        <v>0.6742</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0203</v>
+        <v>-1.0516</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1157</v>
+        <v>1.7258</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4882</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3661</v>
+        <v>-2.2462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1221</v>
+        <v>1.6116</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6478</v>
+        <v>1.3089</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6542</v>
+        <v>1.1946</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0064</v>
+        <v>0.1142</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.193</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3213</v>
+        <v>2.3957</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9188</v>
+        <v>1.6634</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4025</v>
+        <v>0.7323</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.1278</v>
+        <v>0.3281</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3281</v>
+        <v>1.228</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7997</v>
+        <v>-0.8999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CARRETERO GARCÍA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2117</v>
+        <v>0.6021</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8058</v>
+        <v>0.7133</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5941</v>
+        <v>-0.1112</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7075</v>
+        <v>2.136</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8341</v>
+        <v>2.0203</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5416</v>
+        <v>0.1157</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3961</v>
+        <v>1.4882</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4347</v>
+        <v>1.3661</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9614</v>
+        <v>0.1221</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6886</v>
+        <v>0.6478</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2688</v>
+        <v>0.6542</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4199</v>
+        <v>-0.0064</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.579</v>
+        <v>-0.193</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3511</v>
+        <v>0.772</v>
       </c>
       <c r="S9" t="n">
-        <v>0.041</v>
+        <v>0.7869</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3398</v>
+        <v>0.5182</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2988</v>
+        <v>0.2687</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0422</v>
+        <v>-2.1278</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0422</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1002</v>
+        <v>0.0268</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6238</v>
+        <v>0.7239</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.724</v>
+        <v>-0.6972</v>
       </c>
       <c r="G10" t="n">
         <v>0.4799</v>
@@ -1234,13 +1234,13 @@
         <v>0.579</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8732</v>
+        <v>-0.7463</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3569</v>
+        <v>-0.2568</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5162</v>
+        <v>-0.4895</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7121</v>
+        <v>-2.6863</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5501</v>
+        <v>-2.1495</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.162</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.9499</v>
@@ -1312,13 +1312,13 @@
         <v>2.3161</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3609</v>
+        <v>0.3867</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0026</v>
+        <v>0.3979</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3635</v>
+        <v>-0.0113</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5138</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9728</v>
+        <v>-2.6922</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0025</v>
+        <v>-1.8022</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-0.89</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5172</v>
@@ -1390,13 +1390,13 @@
         <v>0.772</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2975</v>
+        <v>-1.0169</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4164</v>
+        <v>-0.2161</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8811</v>
+        <v>-0.8008</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.6187</v>
+        <v>-3.9726</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2356</v>
+        <v>-1.536</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3831</v>
+        <v>-2.4366</v>
       </c>
       <c r="G13" t="n">
         <v>-0.6815</v>
@@ -1468,13 +1468,13 @@
         <v>0.579</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.4491</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3107</v>
+        <v>0.0103</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4059</v>
+        <v>-0.4594</v>
       </c>
       <c r="V13" t="n">
         <v>-2.4559</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>26.051</v>
+        <v>26.0509</v>
       </c>
       <c r="E14" t="n">
-        <v>17.91599999999999</v>
+        <v>17.916</v>
       </c>
       <c r="F14" t="n">
-        <v>8.134999999999998</v>
+        <v>8.135299999999997</v>
       </c>
       <c r="G14" t="n">
         <v>25.4251</v>
@@ -1546,13 +1546,13 @@
         <v>15.4405</v>
       </c>
       <c r="S14" t="n">
-        <v>5.869499999999999</v>
+        <v>5.869600000000002</v>
       </c>
       <c r="T14" t="n">
-        <v>5.770599999999999</v>
+        <v>5.7705</v>
       </c>
       <c r="U14" t="n">
-        <v>0.09879999999999994</v>
+        <v>0.09879999999999983</v>
       </c>
       <c r="V14" t="n">
         <v>-3.313600000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2171</v>
+        <v>2.0579</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0154</v>
+        <v>3.6163</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7983</v>
+        <v>-1.5584</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8266</v>
@@ -1624,13 +1624,13 @@
         <v>2.7021</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8442</v>
+        <v>-1.0034</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0271</v>
+        <v>-0.4263</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.5770999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>1.1857</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6024</v>
+        <v>0.1807</v>
       </c>
       <c r="E16" t="n">
-        <v>3.62</v>
+        <v>3.5198</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.0175</v>
+        <v>-3.3391</v>
       </c>
       <c r="G16" t="n">
         <v>-0.1852</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5294</v>
+        <v>0.1077</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1164</v>
+        <v>0.0162</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4131</v>
+        <v>0.0915</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8999</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.091</v>
+        <v>-1.3313</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1096</v>
+        <v>-0.5101</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9815</v>
+        <v>-0.8212</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8401</v>
@@ -1780,13 +1780,13 @@
         <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>1.205</v>
+        <v>0.9647</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4238</v>
+        <v>1.0232</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2188</v>
+        <v>-0.0585</v>
       </c>
       <c r="V17" t="n">
         <v>-1.228</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0172</v>
+        <v>-1.4689</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7641</v>
+        <v>-0.5638</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2531</v>
+        <v>-0.9051</v>
       </c>
       <c r="G18" t="n">
         <v>-2.3178</v>
@@ -1858,13 +1858,13 @@
         <v>1.3511</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3483</v>
+        <v>0.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3543</v>
+        <v>0.5546</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7026</v>
+        <v>-0.3546</v>
       </c>
       <c r="V18" t="n">
         <v>1.228</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5706</v>
+        <v>-1.7755</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8434</v>
+        <v>-0.7433</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7272</v>
+        <v>-1.0322</v>
       </c>
       <c r="G19" t="n">
         <v>-4.5964</v>
@@ -1936,13 +1936,13 @@
         <v>2.8951</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9439</v>
+        <v>-1.1488</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4045</v>
+        <v>-0.3043</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.5395</v>
+        <v>-0.8444</v>
       </c>
       <c r="V19" t="n">
         <v>3.9698</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>E. GANDARILLAS GARMENDIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6002</v>
+        <v>-2.4273</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0155</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5847</v>
+        <v>-1.4803</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1674</v>
+        <v>-0.5262</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3941</v>
+        <v>-0.3912</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7733</v>
+        <v>-0.135</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2858</v>
+        <v>1.6022</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8798</v>
+        <v>1.0245</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5941</v>
+        <v>0.5777</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8817</v>
+        <v>-2.1283</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5143</v>
+        <v>-1.4157</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3674</v>
+        <v>-0.7126</v>
       </c>
       <c r="P20" t="n">
-        <v>0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.965</v>
+        <v>-3.8602</v>
       </c>
       <c r="R20" t="n">
-        <v>1.158</v>
+        <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6022</v>
+        <v>-0.7201</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2353</v>
+        <v>-0.2029</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3668</v>
+        <v>-0.5173</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.228</v>
+        <v>0.9421</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>-0.5717</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GANDARILLAS GARMENDIA</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.162</v>
+        <v>-3.0546</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5479</v>
+        <v>-1.416</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6141</v>
+        <v>-1.6386</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5262</v>
+        <v>-2.1674</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3912</v>
+        <v>-1.3941</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.135</v>
+        <v>-0.7733</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6022</v>
+        <v>-0.2858</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0245</v>
+        <v>-0.8798</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5777</v>
+        <v>0.5941</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.1283</v>
+        <v>-1.8817</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4157</v>
+        <v>-0.5143</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7126</v>
+        <v>-1.3674</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.1231</v>
+        <v>0.193</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.8602</v>
+        <v>-0.965</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7371</v>
+        <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4548</v>
+        <v>0.1477</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8037</v>
+        <v>-0.1652</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6511</v>
+        <v>0.313</v>
       </c>
       <c r="V21" t="n">
-        <v>0.9421</v>
+        <v>-1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5717</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CONTRERAS MARTINEZ</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3627</v>
+        <v>-3.9972</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5081</v>
+        <v>-2.8693</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8546</v>
+        <v>-1.1279</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.9424</v>
+        <v>-3.518</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8364</v>
+        <v>-2.0792</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.106</v>
+        <v>-1.4388</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8</v>
+        <v>-1.1296</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3724</v>
+        <v>-1.211</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1724</v>
+        <v>0.0814</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.1423</v>
+        <v>-2.3884</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2087</v>
+        <v>-0.8682</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9336</v>
+        <v>-1.5202</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5441</v>
+        <v>2.1231</v>
       </c>
       <c r="S22" t="n">
-        <v>0.007900000000000001</v>
+        <v>-1.3514</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0206</v>
+        <v>-0.7746</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0127</v>
+        <v>-0.5767</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.0422</v>
+        <v>-0.2859</v>
       </c>
       <c r="W22" t="n">
-        <v>0.2014</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2436</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. CONTRERAS MARTINEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.451</v>
+        <v>-4.8168</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2699</v>
+        <v>-2.3093</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1811</v>
+        <v>-2.5075</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.518</v>
+        <v>-3.9424</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0792</v>
+        <v>-0.8364</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4388</v>
+        <v>-3.106</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1296</v>
+        <v>-0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.211</v>
+        <v>0.3724</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0814</v>
+        <v>-1.1724</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.3884</v>
+        <v>-3.1423</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8682</v>
+        <v>-1.2087</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.5202</v>
+        <v>-1.9336</v>
       </c>
       <c r="P23" t="n">
-        <v>1.158</v>
+        <v>-0.386</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8052</v>
+        <v>-0.4462</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1752</v>
+        <v>0.2195</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.63</v>
+        <v>-0.6656</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2859</v>
+        <v>-0.0422</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2014</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2859</v>
+        <v>-0.2436</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6158</v>
+        <v>-7.4152</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.712</v>
+        <v>-5.9122</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9038</v>
+        <v>-1.5029</v>
       </c>
       <c r="G24" t="n">
         <v>-5.505</v>
@@ -2326,13 +2326,13 @@
         <v>1.9301</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8176</v>
+        <v>-0.617</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1613</v>
+        <v>-0.039</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9789</v>
+        <v>-0.578</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3281</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-26.051</v>
+        <v>-24.0482</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.1351</v>
+        <v>-8.135</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.9159</v>
+        <v>-15.9132</v>
       </c>
       <c r="G25" t="n">
         <v>-25.4251</v>
@@ -2377,7 +2377,7 @@
         <v>-12.974</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.9378000000000002</v>
+        <v>-0.9378</v>
       </c>
       <c r="K25" t="n">
         <v>-1.0986</v>
@@ -2404,19 +2404,19 @@
         <v>17.3707</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.869499999999999</v>
+        <v>-3.8668</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.09879999999999989</v>
+        <v>-0.09880000000000011</v>
       </c>
       <c r="U25" t="n">
-        <v>-5.7707</v>
+        <v>-3.7677</v>
       </c>
       <c r="V25" t="n">
-        <v>3.313500000000001</v>
+        <v>3.3135</v>
       </c>
       <c r="W25" t="n">
-        <v>8.342400000000001</v>
+        <v>8.3424</v>
       </c>
       <c r="X25" t="n">
         <v>-5.028799999999999</v>
